--- a/output/2026-09-07_05_Slovenia_Obalno-kraska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-07_05_Slovenia_Obalno-kraska_Depolverazione_Trattamento_aria.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Verificato tramite WebSearch (fonti: karcher.com, ifix.si, firmasi.si, karcher-kusljan.si). Sede di Koper confermata all'indirizzo Ulica 15. maja 18, 6000 Koper - Capodistria, gestita da Kärcher center Kušljan d.o.o. (sede legale a Šmalčja vas 59, 8310 Šentjernej). Punto vendita e servizio assistenza per aspiratori industriali/professionali e attrezzature per pulizia industriale: match diretto per il settore Depolverazione/Trattamento aria.</t>
+          <t>Verificato tramite WebSearch (fonti: karcher.com, ifix.si, firmasi.si, karcher-kusljan.si). Sede di Koper confermata all'indirizzo Ulica 15. maja 18, 6000 Koper - Capodistria, gestita da Kärcher center Kušljan d.o.o. (sede legale a Šmalčja vas 59, 8310 Šentjernej). Punto vendita e servizio assistenza per aspiratori industriali/professionali e attrezzature per pulizia industriale: match diretto per il settore Depolverazione/Trattamento aria. [DUPLICATO — vedi anche: 2026-09-06_14_Slovenia_Jugovzhodna_Slovenija_Metalworking.xlsx]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
